--- a/diseases/d095/2005-2009.xlsx
+++ b/diseases/d095/2005-2009.xlsx
@@ -776,6 +776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -924,6 +929,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1072,6 +1082,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1220,6 +1235,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1368,6 +1388,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1516,6 +1541,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1664,6 +1694,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1812,6 +1847,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1960,6 +2000,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2108,6 +2153,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2256,6 +2306,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2404,6 +2459,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2552,6 +2612,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2700,6 +2765,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2848,6 +2918,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2996,6 +3071,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3144,6 +3224,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3292,6 +3377,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3440,6 +3530,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3588,6 +3683,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3736,6 +3836,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3884,6 +3989,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4032,6 +4142,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4180,6 +4295,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4328,6 +4448,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4476,6 +4601,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4624,6 +4754,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4772,6 +4907,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4920,6 +5060,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5068,6 +5213,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5216,6 +5366,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5364,6 +5519,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5512,6 +5672,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5660,6 +5825,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5808,6 +5978,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5956,6 +6131,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6104,6 +6284,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6252,6 +6437,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6400,6 +6590,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6548,6 +6743,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6696,6 +6896,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6844,6 +7049,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6992,6 +7202,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7140,6 +7355,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7288,6 +7508,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7436,6 +7661,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7584,6 +7814,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7732,6 +7967,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7880,6 +8120,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8028,6 +8273,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8176,6 +8426,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8324,6 +8579,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8472,6 +8732,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8620,6 +8885,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8768,6 +9038,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8916,6 +9191,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9064,6 +9344,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9212,6 +9497,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9360,6 +9650,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9508,6 +9803,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9656,6 +9956,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9804,6 +10109,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO63" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9952,6 +10262,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10100,6 +10415,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO65" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10248,6 +10568,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO66" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10396,6 +10721,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10544,6 +10874,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO68" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10692,6 +11027,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO69" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10840,6 +11180,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO70" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10988,6 +11333,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO71" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11136,6 +11486,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11284,6 +11639,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO73" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11432,6 +11792,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO74" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11580,6 +11945,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO75" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11728,6 +12098,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO76" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11876,6 +12251,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO77" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12024,6 +12404,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO78" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12172,6 +12557,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO79" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12320,6 +12710,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO80" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12468,6 +12863,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO81" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12616,6 +13016,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO82" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12764,6 +13169,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO83" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12912,6 +13322,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO84" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13060,6 +13475,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO85" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13208,6 +13628,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO86" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13356,6 +13781,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO87" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13504,6 +13934,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13652,6 +14087,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO89" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13800,6 +14240,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13948,6 +14393,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14096,6 +14546,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO92" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14244,6 +14699,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO93" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14392,6 +14852,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO94" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14540,6 +15005,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO95" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14688,6 +15158,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO96" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14836,6 +15311,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO97" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14984,6 +15464,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO98" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15132,6 +15617,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO99" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15280,6 +15770,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO100" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15428,6 +15923,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO101" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15576,6 +16076,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO102" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15724,6 +16229,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO103" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15872,6 +16382,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO104" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16020,6 +16535,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO105" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16168,6 +16688,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO106" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16316,6 +16841,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO107" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16464,6 +16994,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO108" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16612,6 +17147,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO109" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16760,6 +17300,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO110" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16908,6 +17453,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO111" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17056,6 +17606,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO112" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17204,6 +17759,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO113" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17352,6 +17912,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO114" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17500,6 +18065,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO115" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17648,6 +18218,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO116" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17796,6 +18371,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO117" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17944,6 +18524,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO118" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18092,6 +18677,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO119" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18240,6 +18830,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO120" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18388,6 +18983,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO121" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18536,6 +19136,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO122" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18684,6 +19289,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO123" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18832,6 +19442,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO124" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18980,6 +19595,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO125" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19128,6 +19748,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO126" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19276,6 +19901,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO127" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19424,6 +20054,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO128" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19572,6 +20207,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO129" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19720,6 +20360,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO130" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19868,6 +20513,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO131" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20016,6 +20666,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO132" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20164,6 +20819,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO133" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20312,6 +20972,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO134" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20460,6 +21125,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO135" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20608,6 +21278,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO136" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20756,6 +21431,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO137" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20904,6 +21584,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO138" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21052,6 +21737,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO139" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21200,6 +21890,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO140" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21348,6 +22043,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO141" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21496,6 +22196,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO142" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21644,6 +22349,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO143" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21792,6 +22502,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO144" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21940,6 +22655,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO145" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22088,6 +22808,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO146" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22236,6 +22961,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO147" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22384,6 +23114,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO148" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22532,6 +23267,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO149" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22680,6 +23420,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO150" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22828,6 +23573,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO151" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22976,6 +23726,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO152" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23124,6 +23879,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO153" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23272,6 +24032,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO154" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23420,6 +24185,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO155" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23568,6 +24338,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO156" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23716,6 +24491,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO157" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23864,6 +24644,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO158" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24012,6 +24797,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO159" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24160,6 +24950,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO160" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24308,6 +25103,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO161" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24456,6 +25256,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO162" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24604,6 +25409,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO163" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24752,6 +25562,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO164" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24900,6 +25715,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO165" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25048,6 +25868,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO166" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25196,6 +26021,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO167" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25344,6 +26174,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO168" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25492,6 +26327,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO169" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25640,6 +26480,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO170" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25788,6 +26633,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO171" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25936,6 +26786,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO172" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26084,6 +26939,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO173" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26232,6 +27092,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO174" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26380,6 +27245,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO175" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26528,6 +27398,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO176" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26676,6 +27551,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO177" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26824,6 +27704,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO178" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26972,6 +27857,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO179" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27120,6 +28010,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO180" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27268,6 +28163,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO181" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27416,6 +28316,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA182" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO182" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27564,6 +28469,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA183" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO183" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27712,6 +28622,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO184" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27860,6 +28775,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO185" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28008,6 +28928,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO186" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28156,6 +29081,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO187" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28304,6 +29234,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO188" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28452,6 +29387,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA189" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO189" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28600,6 +29540,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA190" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO190" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28748,6 +29693,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA191" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO191" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28896,6 +29846,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO192" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29044,6 +29999,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO193" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29192,6 +30152,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO194" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29340,6 +30305,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO195" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29488,6 +30458,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO196" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29636,6 +30611,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA197" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO197" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29784,6 +30764,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO198" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29932,6 +30917,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO199" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30080,6 +31070,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO200" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30228,6 +31223,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA201" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO201" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30376,6 +31376,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA202" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO202" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30524,6 +31529,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA203" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO203" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30672,6 +31682,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO204" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30820,6 +31835,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA205" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO205" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30968,6 +31988,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA206" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO206" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31116,6 +32141,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO207" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31262,6 +32292,11 @@
       <c r="S208" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA208" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO208" t="inlineStr">

--- a/diseases/d095/2005-2009.xlsx
+++ b/diseases/d095/2005-2009.xlsx
@@ -774,11 +774,6 @@
       <c r="R2" t="n">
         <v>0.004686502922966015</v>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U2" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -796,17 +791,7 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -815,12 +800,7 @@
         </is>
       </c>
       <c r="AT2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
@@ -944,11 +924,6 @@
       <c r="R3" t="n">
         <v>0.01506375939524791</v>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U3" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -966,17 +941,7 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -985,12 +950,7 @@
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
@@ -1114,11 +1074,6 @@
       <c r="R4" t="n">
         <v>0.005690753549315876</v>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U4" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -1136,17 +1091,7 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1155,12 +1100,7 @@
         </is>
       </c>
       <c r="AT4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
@@ -1284,11 +1224,6 @@
       <c r="R5" t="n">
         <v>0.01874601169186406</v>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U5" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -1306,17 +1241,7 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -1325,12 +1250,7 @@
         </is>
       </c>
       <c r="AT5" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
@@ -1454,11 +1374,6 @@
       <c r="R6" t="n">
         <v>0.007364504593232309</v>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U6" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -1476,17 +1391,7 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -1495,12 +1400,7 @@
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
@@ -1624,11 +1524,6 @@
       <c r="R7" t="n">
         <v>0.005356003340532588</v>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U7" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -1646,17 +1541,7 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -1665,12 +1550,7 @@
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
@@ -1794,11 +1674,6 @@
       <c r="R8" t="n">
         <v>0.01305525814254818</v>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U8" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -1816,17 +1691,7 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -1835,12 +1700,7 @@
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
@@ -1964,11 +1824,6 @@
       <c r="R9" t="n">
         <v>0.01841126148308077</v>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U9" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -1986,17 +1841,7 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -2005,12 +1850,7 @@
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
@@ -2134,11 +1974,6 @@
       <c r="R10" t="n">
         <v>0.04351752714182728</v>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U10" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -2156,17 +1991,7 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -2175,12 +2000,7 @@
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
@@ -2304,11 +2124,6 @@
       <c r="R11" t="n">
         <v>0.04251327651547742</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U11" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -2326,17 +2141,7 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -2345,12 +2150,7 @@
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
@@ -2474,11 +2274,6 @@
       <c r="R12" t="n">
         <v>0.005356003340532588</v>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U12" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -2496,17 +2291,7 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -2515,12 +2300,7 @@
         </is>
       </c>
       <c r="AT12" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
@@ -2644,11 +2424,6 @@
       <c r="R13" t="n">
         <v>0.04351752714182728</v>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U13" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -2666,17 +2441,7 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ13" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -2685,12 +2450,7 @@
         </is>
       </c>
       <c r="AT13" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
@@ -2814,11 +2574,6 @@
       <c r="R14" t="n">
         <v>0.06527629071274092</v>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U14" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -2836,17 +2591,7 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ14" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -2855,12 +2600,7 @@
         </is>
       </c>
       <c r="AT14" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
@@ -2984,11 +2724,6 @@
       <c r="R15" t="n">
         <v>0.02979276858171253</v>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U15" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -3006,17 +2741,7 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ15" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -3025,12 +2750,7 @@
         </is>
       </c>
       <c r="AT15" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -3154,11 +2874,6 @@
       <c r="R16" t="n">
         <v>0.03782677359251141</v>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U16" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -3176,17 +2891,7 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ16" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -3195,12 +2900,7 @@
         </is>
       </c>
       <c r="AT16" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
@@ -3324,11 +3024,6 @@
       <c r="R17" t="n">
         <v>0.04017002505399441</v>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U17" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -3346,17 +3041,7 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ17" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -3365,12 +3050,7 @@
         </is>
       </c>
       <c r="AT17" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
@@ -3494,11 +3174,6 @@
       <c r="R18" t="n">
         <v>0.1007598128437693</v>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U18" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -3516,17 +3191,7 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ18" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -3535,12 +3200,7 @@
         </is>
       </c>
       <c r="AT18" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
@@ -3664,11 +3324,6 @@
       <c r="R19" t="n">
         <v>0.003012751879049581</v>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U19" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -3686,17 +3341,7 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ19" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -3705,12 +3350,7 @@
         </is>
       </c>
       <c r="AT19" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
@@ -3834,11 +3474,6 @@
       <c r="R20" t="n">
         <v>0.02644526649387966</v>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U20" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -3856,17 +3491,7 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ20" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -3875,12 +3500,7 @@
         </is>
       </c>
       <c r="AT20" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
@@ -4004,11 +3624,6 @@
       <c r="R21" t="n">
         <v>0.004351752714182728</v>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U21" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -4026,17 +3641,7 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ21" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -4045,12 +3650,7 @@
         </is>
       </c>
       <c r="AT21" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
@@ -4174,11 +3774,6 @@
       <c r="R22" t="n">
         <v>0.03682252296616154</v>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U22" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -4196,17 +3791,7 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ22" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -4215,12 +3800,7 @@
         </is>
       </c>
       <c r="AT22" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
@@ -4344,11 +3924,6 @@
       <c r="R23" t="n">
         <v>0.02075451294456378</v>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U23" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -4366,17 +3941,7 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ23" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -4385,12 +3950,7 @@
         </is>
       </c>
       <c r="AT23" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
@@ -4514,11 +4074,6 @@
       <c r="R24" t="n">
         <v>0.05389478361410917</v>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U24" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -4536,17 +4091,7 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ24" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR24" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
@@ -4555,12 +4100,7 @@
         </is>
       </c>
       <c r="AT24" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU24" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
@@ -4684,11 +4224,6 @@
       <c r="R25" t="n">
         <v>0.002343251461483007</v>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U25" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -4706,17 +4241,7 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ25" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR25" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
@@ -4725,12 +4250,7 @@
         </is>
       </c>
       <c r="AT25" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU25" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
@@ -4854,11 +4374,6 @@
       <c r="R26" t="n">
         <v>0.005356003340532588</v>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U26" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -4876,17 +4391,7 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ26" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR26" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
@@ -4895,12 +4400,7 @@
         </is>
       </c>
       <c r="AT26" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU26" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
@@ -5024,11 +4524,6 @@
       <c r="R27" t="n">
         <v>0.005356003340532588</v>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U27" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -5046,17 +4541,7 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ27" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR27" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
@@ -5065,12 +4550,7 @@
         </is>
       </c>
       <c r="AT27" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU27" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
@@ -5194,11 +4674,6 @@
       <c r="R28" t="n">
         <v>0.004017002505399441</v>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U28" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -5216,17 +4691,7 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ28" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR28" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
@@ -5235,12 +4700,7 @@
         </is>
       </c>
       <c r="AT28" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU28" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
@@ -5364,11 +4824,6 @@
       <c r="R29" t="n">
         <v>0.02510626565874651</v>
       </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U29" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -5386,17 +4841,7 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ29" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR29" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr">
@@ -5405,12 +4850,7 @@
         </is>
       </c>
       <c r="AT29" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU29" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
@@ -5534,11 +4974,6 @@
       <c r="R30" t="n">
         <v>0.01740701085673091</v>
       </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U30" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -5556,17 +4991,7 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ30" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR30" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr">
@@ -5575,12 +5000,7 @@
         </is>
       </c>
       <c r="AT30" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU30" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
@@ -5704,11 +5124,6 @@
       <c r="R31" t="n">
         <v>0.01908076190064735</v>
       </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U31" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -5726,17 +5141,7 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ31" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR31" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr">
@@ -5745,12 +5150,7 @@
         </is>
       </c>
       <c r="AT31" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU31" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
@@ -5874,11 +5274,6 @@
       <c r="R32" t="n">
         <v>0.03916577442764455</v>
       </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U32" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -5896,17 +5291,7 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ32" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR32" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr">
@@ -5915,12 +5300,7 @@
         </is>
       </c>
       <c r="AT32" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU32" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
@@ -6044,11 +5424,6 @@
       <c r="R33" t="n">
         <v>0.05623803507559218</v>
       </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U33" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -6066,17 +5441,7 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ33" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR33" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr">
@@ -6085,12 +5450,7 @@
         </is>
       </c>
       <c r="AT33" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU33" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
@@ -6214,11 +5574,6 @@
       <c r="R34" t="n">
         <v>0.03380977108711197</v>
       </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U34" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -6236,17 +5591,7 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ34" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR34" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr">
@@ -6255,12 +5600,7 @@
         </is>
       </c>
       <c r="AT34" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU34" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
@@ -6384,11 +5724,6 @@
       <c r="R35" t="n">
         <v>0.03816152380129469</v>
       </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U35" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -6406,17 +5741,7 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ35" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR35" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr">
@@ -6425,12 +5750,7 @@
         </is>
       </c>
       <c r="AT35" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU35" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
@@ -6554,11 +5874,6 @@
       <c r="R36" t="n">
         <v>0.007364504593232309</v>
       </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U36" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -6576,17 +5891,7 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ36" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR36" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr">
@@ -6595,12 +5900,7 @@
         </is>
       </c>
       <c r="AT36" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU36" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
@@ -6724,11 +6024,6 @@
       <c r="R37" t="n">
         <v>0.01908076190064735</v>
       </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U37" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -6746,17 +6041,7 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ37" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR37" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr">
@@ -6765,12 +6050,7 @@
         </is>
       </c>
       <c r="AT37" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU37" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
@@ -6894,11 +6174,6 @@
       <c r="R38" t="n">
         <v>0.03046226899927909</v>
       </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U38" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -6916,17 +6191,7 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ38" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR38" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr">
@@ -6935,12 +6200,7 @@
         </is>
       </c>
       <c r="AT38" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU38" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
@@ -7064,11 +6324,6 @@
       <c r="R39" t="n">
         <v>0.04083952547156099</v>
       </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U39" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -7086,17 +6341,7 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ39" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR39" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr">
@@ -7105,12 +6350,7 @@
         </is>
       </c>
       <c r="AT39" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU39" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV39" t="inlineStr">
         <is>
@@ -7234,11 +6474,6 @@
       <c r="R40" t="n">
         <v>0.0254410158675298</v>
       </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U40" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -7256,17 +6491,7 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ40" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR40" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr">
@@ -7275,12 +6500,7 @@
         </is>
       </c>
       <c r="AT40" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU40" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV40" t="inlineStr">
         <is>
@@ -7404,11 +6624,6 @@
       <c r="R41" t="n">
         <v>0.003347502087832868</v>
       </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U41" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -7426,17 +6641,7 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ41" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR41" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr">
@@ -7445,12 +6650,7 @@
         </is>
       </c>
       <c r="AT41" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU41" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV41" t="inlineStr">
         <is>
@@ -7574,11 +6774,6 @@
       <c r="R42" t="n">
         <v>0.02075451294456378</v>
       </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U42" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -7596,17 +6791,7 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ42" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR42" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr">
@@ -7615,12 +6800,7 @@
         </is>
       </c>
       <c r="AT42" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU42" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
@@ -7744,11 +6924,6 @@
       <c r="R43" t="n">
         <v>0.02744951712022952</v>
       </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U43" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -7766,17 +6941,7 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ43" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR43" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr">
@@ -7785,12 +6950,7 @@
         </is>
       </c>
       <c r="AT43" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU43" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
@@ -7914,11 +7074,6 @@
       <c r="R44" t="n">
         <v>0.03682252296616154</v>
       </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U44" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -7936,17 +7091,7 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ44" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR44" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr">
@@ -7955,12 +7100,7 @@
         </is>
       </c>
       <c r="AT44" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU44" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
@@ -8084,11 +7224,6 @@
       <c r="R45" t="n">
         <v>0.04619552881209357</v>
       </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U45" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -8106,17 +7241,7 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ45" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR45" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr">
@@ -8125,12 +7250,7 @@
         </is>
       </c>
       <c r="AT45" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU45" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
@@ -8254,11 +7374,6 @@
       <c r="R46" t="n">
         <v>0.04385227735061056</v>
       </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U46" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -8276,17 +7391,7 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ46" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR46" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr">
@@ -8295,12 +7400,7 @@
         </is>
       </c>
       <c r="AT46" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU46" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV46" t="inlineStr">
         <is>
@@ -8424,11 +7524,6 @@
       <c r="R47" t="n">
         <v>0.04385227735061056</v>
       </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U47" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -8446,17 +7541,7 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ47" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR47" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr">
@@ -8465,12 +7550,7 @@
         </is>
       </c>
       <c r="AT47" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU47" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV47" t="inlineStr">
         <is>
@@ -8594,11 +7674,6 @@
       <c r="R48" t="n">
         <v>0.02611051628509637</v>
       </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U48" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -8616,17 +7691,7 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ48" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR48" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr">
@@ -8635,12 +7700,7 @@
         </is>
       </c>
       <c r="AT48" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU48" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV48" t="inlineStr">
         <is>
@@ -8764,11 +7824,6 @@
       <c r="R49" t="n">
         <v>0.05121678194384288</v>
       </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U49" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -8786,17 +7841,7 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ49" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR49" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr">
@@ -8805,12 +7850,7 @@
         </is>
       </c>
       <c r="AT49" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU49" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
@@ -8934,11 +7974,6 @@
       <c r="R50" t="n">
         <v>0.07063229405327351</v>
       </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U50" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -8956,17 +7991,7 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ50" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR50" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr">
@@ -8975,12 +8000,7 @@
         </is>
       </c>
       <c r="AT50" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU50" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV50" t="inlineStr">
         <is>
@@ -9104,11 +8124,6 @@
       <c r="R51" t="n">
         <v>0.06025503758099162</v>
       </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U51" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -9126,17 +8141,7 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ51" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR51" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr">
@@ -9145,12 +8150,7 @@
         </is>
       </c>
       <c r="AT51" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU51" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV51" t="inlineStr">
         <is>
@@ -9274,11 +8274,6 @@
       <c r="R52" t="n">
         <v>0.045526028394527</v>
       </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U52" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -9296,17 +8291,7 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ52" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR52" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr">
@@ -9315,12 +8300,7 @@
         </is>
       </c>
       <c r="AT52" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU52" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV52" t="inlineStr">
         <is>
@@ -9444,11 +8424,6 @@
       <c r="R53" t="n">
         <v>0.02811901753779609</v>
       </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U53" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -9466,17 +8441,7 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ53" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR53" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr">
@@ -9485,12 +8450,7 @@
         </is>
       </c>
       <c r="AT53" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU53" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
@@ -9614,11 +8574,6 @@
       <c r="R54" t="n">
         <v>0.01424575869515847</v>
       </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U54" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -9636,17 +8591,7 @@
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ54" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR54" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr">
@@ -9655,12 +8600,7 @@
         </is>
       </c>
       <c r="AT54" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU54" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV54" t="inlineStr">
         <is>
@@ -9784,11 +8724,6 @@
       <c r="R55" t="n">
         <v>0.03213578124256679</v>
       </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U55" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -9806,17 +8741,7 @@
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ55" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR55" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr">
@@ -9825,12 +8750,7 @@
         </is>
       </c>
       <c r="AT55" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU55" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
@@ -9954,11 +8874,6 @@
       <c r="R56" t="n">
         <v>0.03047929767336231</v>
       </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U56" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -9976,17 +8891,7 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ56" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR56" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr">
@@ -9995,12 +8900,7 @@
         </is>
       </c>
       <c r="AT56" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU56" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
@@ -10124,11 +9024,6 @@
       <c r="R57" t="n">
         <v>0.06791582633738341</v>
       </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U57" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -10146,17 +9041,7 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ57" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR57" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr">
@@ -10165,12 +9050,7 @@
         </is>
       </c>
       <c r="AT57" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU57" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
@@ -10294,11 +9174,6 @@
       <c r="R58" t="n">
         <v>0.02584114367958979</v>
       </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U58" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -10316,17 +9191,7 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ58" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR58" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr">
@@ -10335,12 +9200,7 @@
         </is>
       </c>
       <c r="AT58" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU58" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV58" t="inlineStr">
         <is>
@@ -10464,11 +9324,6 @@
       <c r="R59" t="n">
         <v>0.02186558311349905</v>
       </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U59" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -10486,17 +9341,7 @@
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ59" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR59" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr">
@@ -10505,12 +9350,7 @@
         </is>
       </c>
       <c r="AT59" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU59" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
@@ -10634,11 +9474,6 @@
       <c r="R60" t="n">
         <v>0.01822131926124921</v>
       </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U60" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -10656,17 +9491,7 @@
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ60" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR60" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS60" t="inlineStr">
@@ -10675,12 +9500,7 @@
         </is>
       </c>
       <c r="AT60" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU60" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV60" t="inlineStr">
         <is>
@@ -10804,11 +9624,6 @@
       <c r="R61" t="n">
         <v>0.03843041880554379</v>
       </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U61" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -10826,17 +9641,7 @@
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ61" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR61" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS61" t="inlineStr">
@@ -10845,12 +9650,7 @@
         </is>
       </c>
       <c r="AT61" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU61" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV61" t="inlineStr">
         <is>
@@ -10974,11 +9774,6 @@
       <c r="R62" t="n">
         <v>0.04704413336540705</v>
       </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U62" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -10996,17 +9791,7 @@
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ62" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR62" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS62" t="inlineStr">
@@ -11015,12 +9800,7 @@
         </is>
       </c>
       <c r="AT62" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU62" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV62" t="inlineStr">
         <is>
@@ -11144,11 +9924,6 @@
       <c r="R63" t="n">
         <v>0.04605024322388437</v>
       </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U63" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -11166,17 +9941,7 @@
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ63" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR63" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS63" t="inlineStr">
@@ -11185,12 +9950,7 @@
         </is>
       </c>
       <c r="AT63" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU63" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV63" t="inlineStr">
         <is>
@@ -11314,11 +10074,6 @@
       <c r="R64" t="n">
         <v>0.03809912209170289</v>
       </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U64" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -11336,17 +10091,7 @@
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ64" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR64" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS64" t="inlineStr">
@@ -11355,12 +10100,7 @@
         </is>
       </c>
       <c r="AT64" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU64" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV64" t="inlineStr">
         <is>
@@ -11484,11 +10224,6 @@
       <c r="R65" t="n">
         <v>0.02650373710727158</v>
       </c>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U65" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -11506,17 +10241,7 @@
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ65" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR65" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS65" t="inlineStr">
@@ -11525,12 +10250,7 @@
         </is>
       </c>
       <c r="AT65" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU65" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV65" t="inlineStr">
         <is>
@@ -11654,11 +10374,6 @@
       <c r="R66" t="n">
         <v>0.03677393523633932</v>
       </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U66" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -11676,17 +10391,7 @@
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ66" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR66" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS66" t="inlineStr">
@@ -11695,12 +10400,7 @@
         </is>
       </c>
       <c r="AT66" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU66" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV66" t="inlineStr">
         <is>
@@ -11824,11 +10524,6 @@
       <c r="R67" t="n">
         <v>0.03843041880554379</v>
       </c>
-      <c r="S67" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U67" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -11846,17 +10541,7 @@
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ67" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR67" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS67" t="inlineStr">
@@ -11865,12 +10550,7 @@
         </is>
       </c>
       <c r="AT67" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU67" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV67" t="inlineStr">
         <is>
@@ -11994,11 +10674,6 @@
       <c r="R68" t="n">
         <v>0.04870061693461152</v>
       </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U68" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -12016,17 +10691,7 @@
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ68" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR68" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS68" t="inlineStr">
@@ -12035,12 +10700,7 @@
         </is>
       </c>
       <c r="AT68" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU68" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV68" t="inlineStr">
         <is>
@@ -12164,11 +10824,6 @@
       <c r="R69" t="n">
         <v>0.0437311662269981</v>
       </c>
-      <c r="S69" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U69" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -12186,17 +10841,7 @@
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ69" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR69" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS69" t="inlineStr">
@@ -12205,12 +10850,7 @@
         </is>
       </c>
       <c r="AT69" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU69" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV69" t="inlineStr">
         <is>
@@ -12334,11 +10974,6 @@
       <c r="R70" t="n">
         <v>0.03312967138408947</v>
       </c>
-      <c r="S70" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U70" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -12356,17 +10991,7 @@
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ70" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR70" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS70" t="inlineStr">
@@ -12375,12 +11000,7 @@
         </is>
       </c>
       <c r="AT70" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU70" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV70" t="inlineStr">
         <is>
@@ -12504,11 +11124,6 @@
       <c r="R71" t="n">
         <v>0.02816022067647605</v>
       </c>
-      <c r="S71" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U71" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -12526,17 +11141,7 @@
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ71" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR71" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS71" t="inlineStr">
@@ -12545,12 +11150,7 @@
         </is>
       </c>
       <c r="AT71" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU71" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV71" t="inlineStr">
         <is>
@@ -12674,11 +11274,6 @@
       <c r="R72" t="n">
         <v>0.04207468265779363</v>
       </c>
-      <c r="S72" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U72" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -12696,17 +11291,7 @@
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ72" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR72" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS72" t="inlineStr">
@@ -12715,12 +11300,7 @@
         </is>
       </c>
       <c r="AT72" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU72" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV72" t="inlineStr">
         <is>
@@ -12844,11 +11424,6 @@
       <c r="R73" t="n">
         <v>0.04141208923011185</v>
       </c>
-      <c r="S73" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U73" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -12866,17 +11441,7 @@
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ73" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR73" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS73" t="inlineStr">
@@ -12885,12 +11450,7 @@
         </is>
       </c>
       <c r="AT73" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU73" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV73" t="inlineStr">
         <is>
@@ -13014,11 +11574,6 @@
       <c r="R74" t="n">
         <v>0.03578004509481663</v>
       </c>
-      <c r="S74" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U74" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -13036,17 +11591,7 @@
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ74" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR74" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS74" t="inlineStr">
@@ -13055,12 +11600,7 @@
         </is>
       </c>
       <c r="AT74" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU74" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV74" t="inlineStr">
         <is>
@@ -13184,11 +11724,6 @@
       <c r="R75" t="n">
         <v>0.03511745166713484</v>
       </c>
-      <c r="S75" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U75" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -13206,17 +11741,7 @@
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ75" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR75" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS75" t="inlineStr">
@@ -13225,12 +11750,7 @@
         </is>
       </c>
       <c r="AT75" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU75" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV75" t="inlineStr">
         <is>
@@ -13354,11 +11874,6 @@
       <c r="R76" t="n">
         <v>0.02120298968581726</v>
       </c>
-      <c r="S76" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U76" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -13376,17 +11891,7 @@
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ76" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR76" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS76" t="inlineStr">
@@ -13395,12 +11900,7 @@
         </is>
       </c>
       <c r="AT76" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU76" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV76" t="inlineStr">
         <is>
@@ -13524,11 +12024,6 @@
       <c r="R77" t="n">
         <v>0.05698303478063389</v>
       </c>
-      <c r="S77" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U77" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -13546,17 +12041,7 @@
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ77" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR77" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS77" t="inlineStr">
@@ -13565,12 +12050,7 @@
         </is>
       </c>
       <c r="AT77" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU77" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV77" t="inlineStr">
         <is>
@@ -13694,11 +12174,6 @@
       <c r="R78" t="n">
         <v>0.03279837467024858</v>
       </c>
-      <c r="S78" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U78" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -13716,17 +12191,7 @@
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ78" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR78" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS78" t="inlineStr">
@@ -13735,12 +12200,7 @@
         </is>
       </c>
       <c r="AT78" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU78" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV78" t="inlineStr">
         <is>
@@ -13864,11 +12324,6 @@
       <c r="R79" t="n">
         <v>0.05367006764222494</v>
       </c>
-      <c r="S79" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U79" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -13886,17 +12341,7 @@
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ79" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR79" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS79" t="inlineStr">
@@ -13905,12 +12350,7 @@
         </is>
       </c>
       <c r="AT79" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU79" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV79" t="inlineStr">
         <is>
@@ -14034,11 +12474,6 @@
       <c r="R80" t="n">
         <v>0.03743652866402111</v>
       </c>
-      <c r="S80" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U80" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -14056,17 +12491,7 @@
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ80" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR80" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS80" t="inlineStr">
@@ -14075,12 +12500,7 @@
         </is>
       </c>
       <c r="AT80" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU80" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV80" t="inlineStr">
         <is>
@@ -14204,11 +12624,6 @@
       <c r="R81" t="n">
         <v>0.02948540753183963</v>
       </c>
-      <c r="S81" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U81" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -14226,17 +12641,7 @@
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ81" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR81" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS81" t="inlineStr">
@@ -14245,12 +12650,7 @@
         </is>
       </c>
       <c r="AT81" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU81" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV81" t="inlineStr">
         <is>
@@ -14374,11 +12774,6 @@
       <c r="R82" t="n">
         <v>0.01027019812906774</v>
       </c>
-      <c r="S82" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U82" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -14396,17 +12791,7 @@
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ82" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR82" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS82" t="inlineStr">
@@ -14415,12 +12800,7 @@
         </is>
       </c>
       <c r="AT82" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU82" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV82" t="inlineStr">
         <is>
@@ -14544,11 +12924,6 @@
       <c r="R83" t="n">
         <v>0.04174338594395274</v>
       </c>
-      <c r="S83" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U83" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -14566,17 +12941,7 @@
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ83" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR83" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS83" t="inlineStr">
@@ -14585,12 +12950,7 @@
         </is>
       </c>
       <c r="AT83" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU83" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV83" t="inlineStr">
         <is>
@@ -14714,11 +13074,6 @@
       <c r="R84" t="n">
         <v>0.02385336339654442</v>
       </c>
-      <c r="S84" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U84" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -14736,17 +13091,7 @@
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ84" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR84" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS84" t="inlineStr">
@@ -14755,12 +13100,7 @@
         </is>
       </c>
       <c r="AT84" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU84" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV84" t="inlineStr">
         <is>
@@ -14884,11 +13224,6 @@
       <c r="R85" t="n">
         <v>0.02550984696574889</v>
       </c>
-      <c r="S85" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U85" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -14906,17 +13241,7 @@
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ85" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR85" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS85" t="inlineStr">
@@ -14925,12 +13250,7 @@
         </is>
       </c>
       <c r="AT85" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU85" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV85" t="inlineStr">
         <is>
@@ -15054,11 +13374,6 @@
       <c r="R86" t="n">
         <v>0.02054039625813547</v>
       </c>
-      <c r="S86" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U86" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -15076,17 +13391,7 @@
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ86" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR86" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS86" t="inlineStr">
@@ -15095,12 +13400,7 @@
         </is>
       </c>
       <c r="AT86" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU86" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV86" t="inlineStr">
         <is>
@@ -15224,11 +13524,6 @@
       <c r="R87" t="n">
         <v>0.02716633053495337</v>
       </c>
-      <c r="S87" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U87" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -15246,17 +13541,7 @@
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ87" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR87" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS87" t="inlineStr">
@@ -15265,12 +13550,7 @@
         </is>
       </c>
       <c r="AT87" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU87" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV87" t="inlineStr">
         <is>
@@ -15394,11 +13674,6 @@
       <c r="R88" t="n">
         <v>0.03611134180865752</v>
       </c>
-      <c r="S88" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U88" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -15416,17 +13691,7 @@
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ88" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR88" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS88" t="inlineStr">
@@ -15435,12 +13700,7 @@
         </is>
       </c>
       <c r="AT88" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU88" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV88" t="inlineStr">
         <is>
@@ -15564,11 +13824,6 @@
       <c r="R89" t="n">
         <v>0.01557094555052205</v>
       </c>
-      <c r="S89" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U89" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -15586,17 +13841,7 @@
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ89" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR89" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS89" t="inlineStr">
@@ -15605,12 +13850,7 @@
         </is>
       </c>
       <c r="AT89" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU89" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV89" t="inlineStr">
         <is>
@@ -15734,11 +13974,6 @@
       <c r="R90" t="n">
         <v>0.03677393523633932</v>
       </c>
-      <c r="S90" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U90" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -15756,17 +13991,7 @@
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ90" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR90" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS90" t="inlineStr">
@@ -15775,12 +14000,7 @@
         </is>
       </c>
       <c r="AT90" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU90" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV90" t="inlineStr">
         <is>
@@ -15904,11 +14124,6 @@
       <c r="R91" t="n">
         <v>0.04870061693461152</v>
       </c>
-      <c r="S91" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U91" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -15926,17 +14141,7 @@
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ91" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR91" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS91" t="inlineStr">
@@ -15945,12 +14150,7 @@
         </is>
       </c>
       <c r="AT91" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU91" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV91" t="inlineStr">
         <is>
@@ -16074,11 +14274,6 @@
       <c r="R92" t="n">
         <v>0.02617244039343069</v>
       </c>
-      <c r="S92" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U92" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -16096,17 +14291,7 @@
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ92" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR92" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS92" t="inlineStr">
@@ -16115,12 +14300,7 @@
         </is>
       </c>
       <c r="AT92" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU92" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV92" t="inlineStr">
         <is>
@@ -16244,11 +14424,6 @@
       <c r="R93" t="n">
         <v>0.01789002254740832</v>
       </c>
-      <c r="S93" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U93" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -16266,17 +14441,7 @@
       </c>
       <c r="AP93" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ93" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR93" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS93" t="inlineStr">
@@ -16285,12 +14450,7 @@
         </is>
       </c>
       <c r="AT93" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU93" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV93" t="inlineStr">
         <is>
@@ -16414,11 +14574,6 @@
       <c r="R94" t="n">
         <v>0.02120298968581726</v>
       </c>
-      <c r="S94" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U94" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -16436,17 +14591,7 @@
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ94" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR94" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS94" t="inlineStr">
@@ -16455,12 +14600,7 @@
         </is>
       </c>
       <c r="AT94" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU94" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV94" t="inlineStr">
         <is>
@@ -16584,11 +14724,6 @@
       <c r="R95" t="n">
         <v>0.01755872583356742</v>
       </c>
-      <c r="S95" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U95" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -16606,17 +14741,7 @@
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ95" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR95" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS95" t="inlineStr">
@@ -16625,12 +14750,7 @@
         </is>
       </c>
       <c r="AT95" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU95" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV95" t="inlineStr">
         <is>
@@ -16754,11 +14874,6 @@
       <c r="R96" t="n">
         <v>0.04240597937163453</v>
       </c>
-      <c r="S96" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U96" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -16776,17 +14891,7 @@
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ96" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR96" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS96" t="inlineStr">
@@ -16795,12 +14900,7 @@
         </is>
       </c>
       <c r="AT96" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU96" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV96" t="inlineStr">
         <is>
@@ -16924,11 +15024,6 @@
       <c r="R97" t="n">
         <v>0.04041819908858916</v>
       </c>
-      <c r="S97" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U97" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -16946,17 +15041,7 @@
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ97" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR97" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS97" t="inlineStr">
@@ -16965,12 +15050,7 @@
         </is>
       </c>
       <c r="AT97" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU97" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV97" t="inlineStr">
         <is>
@@ -17094,11 +15174,6 @@
       <c r="R98" t="n">
         <v>0.001325186855363579</v>
       </c>
-      <c r="S98" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U98" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -17116,17 +15191,7 @@
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ98" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR98" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS98" t="inlineStr">
@@ -17135,12 +15200,7 @@
         </is>
       </c>
       <c r="AT98" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU98" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV98" t="inlineStr">
         <is>
@@ -17264,11 +15324,6 @@
       <c r="R99" t="n">
         <v>0.03014800095952142</v>
       </c>
-      <c r="S99" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U99" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -17286,17 +15341,7 @@
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ99" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR99" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS99" t="inlineStr">
@@ -17305,12 +15350,7 @@
         </is>
       </c>
       <c r="AT99" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU99" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV99" t="inlineStr">
         <is>
@@ -17434,11 +15474,6 @@
       <c r="R100" t="n">
         <v>0.02882281410415784</v>
       </c>
-      <c r="S100" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U100" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -17456,17 +15491,7 @@
       </c>
       <c r="AP100" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ100" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR100" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS100" t="inlineStr">
@@ -17475,12 +15500,7 @@
         </is>
       </c>
       <c r="AT100" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU100" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV100" t="inlineStr">
         <is>
@@ -17604,11 +15624,6 @@
       <c r="R101" t="n">
         <v>0.04903191364845242</v>
       </c>
-      <c r="S101" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U101" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -17626,17 +15641,7 @@
       </c>
       <c r="AP101" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ101" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR101" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS101" t="inlineStr">
@@ -17645,12 +15650,7 @@
         </is>
       </c>
       <c r="AT101" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU101" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV101" t="inlineStr">
         <is>
@@ -17774,11 +15774,6 @@
       <c r="R102" t="n">
         <v>0.05333877092838404</v>
       </c>
-      <c r="S102" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U102" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -17796,17 +15791,7 @@
       </c>
       <c r="AP102" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ102" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR102" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS102" t="inlineStr">
@@ -17815,12 +15800,7 @@
         </is>
       </c>
       <c r="AT102" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU102" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV102" t="inlineStr">
         <is>
@@ -17944,11 +15924,6 @@
       <c r="R103" t="n">
         <v>0.04008690237474826</v>
       </c>
-      <c r="S103" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U103" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -17966,17 +15941,7 @@
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ103" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR103" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS103" t="inlineStr">
@@ -17985,12 +15950,7 @@
         </is>
       </c>
       <c r="AT103" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU103" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV103" t="inlineStr">
         <is>
@@ -18114,11 +16074,6 @@
       <c r="R104" t="n">
         <v>0.03975560566090736</v>
       </c>
-      <c r="S104" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U104" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -18136,17 +16091,7 @@
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ104" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR104" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS104" t="inlineStr">
@@ -18155,12 +16100,7 @@
         </is>
       </c>
       <c r="AT104" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU104" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
@@ -18284,11 +16224,6 @@
       <c r="R105" t="n">
         <v>0.02418466011038531</v>
       </c>
-      <c r="S105" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U105" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -18306,17 +16241,7 @@
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ105" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR105" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS105" t="inlineStr">
@@ -18325,12 +16250,7 @@
         </is>
       </c>
       <c r="AT105" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU105" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV105" t="inlineStr">
         <is>
@@ -18454,11 +16374,6 @@
       <c r="R106" t="n">
         <v>0.01377183139609162</v>
       </c>
-      <c r="S106" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U106" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -18476,17 +16391,7 @@
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ106" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR106" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS106" t="inlineStr">
@@ -18495,12 +16400,7 @@
         </is>
       </c>
       <c r="AT106" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU106" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV106" t="inlineStr">
         <is>
@@ -18624,11 +16524,6 @@
       <c r="R107" t="n">
         <v>0.001639503737629955</v>
       </c>
-      <c r="S107" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U107" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -18646,17 +16541,7 @@
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ107" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR107" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS107" t="inlineStr">
@@ -18665,12 +16550,7 @@
         </is>
       </c>
       <c r="AT107" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU107" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV107" t="inlineStr">
         <is>
@@ -18794,11 +16674,6 @@
       <c r="R108" t="n">
         <v>0.03115057101496914</v>
       </c>
-      <c r="S108" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U108" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -18816,17 +16691,7 @@
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ108" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR108" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS108" t="inlineStr">
@@ -18835,12 +16700,7 @@
         </is>
       </c>
       <c r="AT108" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU108" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV108" t="inlineStr">
         <is>
@@ -18964,11 +16824,6 @@
       <c r="R109" t="n">
         <v>0.03902018895559291</v>
       </c>
-      <c r="S109" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U109" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -18986,17 +16841,7 @@
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ109" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR109" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS109" t="inlineStr">
@@ -19005,12 +16850,7 @@
         </is>
       </c>
       <c r="AT109" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU109" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV109" t="inlineStr">
         <is>
@@ -19134,11 +16974,6 @@
       <c r="R110" t="n">
         <v>0.01967404485155946</v>
       </c>
-      <c r="S110" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U110" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -19156,17 +16991,7 @@
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ110" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR110" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS110" t="inlineStr">
@@ -19175,12 +17000,7 @@
         </is>
       </c>
       <c r="AT110" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU110" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV110" t="inlineStr">
         <is>
@@ -19304,11 +17124,6 @@
       <c r="R111" t="n">
         <v>0.02065774709413743</v>
       </c>
-      <c r="S111" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U111" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -19326,17 +17141,7 @@
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ111" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR111" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS111" t="inlineStr">
@@ -19345,12 +17150,7 @@
         </is>
       </c>
       <c r="AT111" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU111" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV111" t="inlineStr">
         <is>
@@ -19474,11 +17274,6 @@
       <c r="R112" t="n">
         <v>0.01737873961887752</v>
       </c>
-      <c r="S112" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U112" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -19496,17 +17291,7 @@
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ112" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR112" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS112" t="inlineStr">
@@ -19515,12 +17300,7 @@
         </is>
       </c>
       <c r="AT112" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU112" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV112" t="inlineStr">
         <is>
@@ -19644,11 +17424,6 @@
       <c r="R113" t="n">
         <v>0.05213621885663255</v>
       </c>
-      <c r="S113" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U113" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -19666,17 +17441,7 @@
       </c>
       <c r="AP113" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ113" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR113" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS113" t="inlineStr">
@@ -19685,12 +17450,7 @@
         </is>
       </c>
       <c r="AT113" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU113" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV113" t="inlineStr">
         <is>
@@ -19814,11 +17574,6 @@
       <c r="R114" t="n">
         <v>0.001967404485155945</v>
       </c>
-      <c r="S114" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U114" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -19836,17 +17591,7 @@
       </c>
       <c r="AP114" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ114" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR114" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS114" t="inlineStr">
@@ -19855,12 +17600,7 @@
         </is>
       </c>
       <c r="AT114" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU114" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV114" t="inlineStr">
         <is>
@@ -19984,11 +17724,6 @@
       <c r="R115" t="n">
         <v>0.02328095307434535</v>
       </c>
-      <c r="S115" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U115" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -20006,17 +17741,7 @@
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ115" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR115" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS115" t="inlineStr">
@@ -20025,12 +17750,7 @@
         </is>
       </c>
       <c r="AT115" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU115" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV115" t="inlineStr">
         <is>
@@ -20154,11 +17874,6 @@
       <c r="R116" t="n">
         <v>0.04393870016848278</v>
       </c>
-      <c r="S116" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U116" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -20176,17 +17891,7 @@
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ116" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR116" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS116" t="inlineStr">
@@ -20195,12 +17900,7 @@
         </is>
       </c>
       <c r="AT116" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU116" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV116" t="inlineStr">
         <is>
@@ -20324,11 +18024,6 @@
       <c r="R117" t="n">
         <v>0.03639698297538499</v>
       </c>
-      <c r="S117" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U117" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -20346,17 +18041,7 @@
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ117" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR117" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS117" t="inlineStr">
@@ -20365,12 +18050,7 @@
         </is>
       </c>
       <c r="AT117" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU117" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV117" t="inlineStr">
         <is>
@@ -20494,11 +18174,6 @@
       <c r="R118" t="n">
         <v>0.01705083887135153</v>
       </c>
-      <c r="S118" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U118" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -20516,17 +18191,7 @@
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ118" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR118" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS118" t="inlineStr">
@@ -20535,12 +18200,7 @@
         </is>
       </c>
       <c r="AT118" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU118" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV118" t="inlineStr">
         <is>
@@ -20664,11 +18324,6 @@
       <c r="R119" t="n">
         <v>0.04000389119817089</v>
       </c>
-      <c r="S119" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U119" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -20686,17 +18341,7 @@
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ119" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR119" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS119" t="inlineStr">
@@ -20705,12 +18350,7 @@
         </is>
       </c>
       <c r="AT119" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU119" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV119" t="inlineStr">
         <is>
@@ -20834,11 +18474,6 @@
       <c r="R120" t="n">
         <v>0.04197129568332684</v>
       </c>
-      <c r="S120" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U120" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -20856,17 +18491,7 @@
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ120" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR120" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS120" t="inlineStr">
@@ -20875,12 +18500,7 @@
         </is>
       </c>
       <c r="AT120" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU120" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV120" t="inlineStr">
         <is>
@@ -21004,11 +18624,6 @@
       <c r="R121" t="n">
         <v>0.03147847176249512</v>
       </c>
-      <c r="S121" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U121" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -21026,17 +18641,7 @@
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ121" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR121" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS121" t="inlineStr">
@@ -21045,12 +18650,7 @@
         </is>
       </c>
       <c r="AT121" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU121" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV121" t="inlineStr">
         <is>
@@ -21174,11 +18774,6 @@
       <c r="R122" t="n">
         <v>0.008853320183201754</v>
       </c>
-      <c r="S122" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U122" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -21196,17 +18791,7 @@
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ122" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR122" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS122" t="inlineStr">
@@ -21215,12 +18800,7 @@
         </is>
       </c>
       <c r="AT122" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU122" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV122" t="inlineStr">
         <is>
@@ -21344,11 +18924,6 @@
       <c r="R123" t="n">
         <v>0.04393870016848278</v>
       </c>
-      <c r="S123" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U123" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -21366,17 +18941,7 @@
       </c>
       <c r="AP123" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ123" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR123" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS123" t="inlineStr">
@@ -21385,12 +18950,7 @@
         </is>
       </c>
       <c r="AT123" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU123" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV123" t="inlineStr">
         <is>
@@ -21514,11 +19074,6 @@
       <c r="R124" t="n">
         <v>0.03442957849022905</v>
       </c>
-      <c r="S124" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U124" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -21536,17 +19091,7 @@
       </c>
       <c r="AP124" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ124" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR124" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS124" t="inlineStr">
@@ -21555,12 +19100,7 @@
         </is>
       </c>
       <c r="AT124" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU124" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV124" t="inlineStr">
         <is>
@@ -21684,11 +19224,6 @@
       <c r="R125" t="n">
         <v>0.03147847176249512</v>
       </c>
-      <c r="S125" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U125" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -21706,17 +19241,7 @@
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ125" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR125" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS125" t="inlineStr">
@@ -21725,12 +19250,7 @@
         </is>
       </c>
       <c r="AT125" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU125" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV125" t="inlineStr">
         <is>
@@ -21854,11 +19374,6 @@
       <c r="R126" t="n">
         <v>0.0252483575595013</v>
       </c>
-      <c r="S126" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U126" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -21876,17 +19391,7 @@
       </c>
       <c r="AP126" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ126" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR126" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS126" t="inlineStr">
@@ -21895,12 +19400,7 @@
         </is>
       </c>
       <c r="AT126" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU126" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV126" t="inlineStr">
         <is>
@@ -22024,11 +19524,6 @@
       <c r="R127" t="n">
         <v>0.02951106727733918</v>
       </c>
-      <c r="S127" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U127" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -22046,17 +19541,7 @@
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ127" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR127" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS127" t="inlineStr">
@@ -22065,12 +19550,7 @@
         </is>
       </c>
       <c r="AT127" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU127" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV127" t="inlineStr">
         <is>
@@ -22194,11 +19674,6 @@
       <c r="R128" t="n">
         <v>0.02360885382187134</v>
       </c>
-      <c r="S128" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U128" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -22216,17 +19691,7 @@
       </c>
       <c r="AP128" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ128" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR128" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS128" t="inlineStr">
@@ -22235,12 +19700,7 @@
         </is>
       </c>
       <c r="AT128" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU128" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV128" t="inlineStr">
         <is>
@@ -22364,11 +19824,6 @@
       <c r="R129" t="n">
         <v>0.04065969269322287</v>
       </c>
-      <c r="S129" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U129" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -22386,17 +19841,7 @@
       </c>
       <c r="AP129" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ129" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR129" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS129" t="inlineStr">
@@ -22405,12 +19850,7 @@
         </is>
       </c>
       <c r="AT129" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU129" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV129" t="inlineStr">
         <is>
@@ -22534,11 +19974,6 @@
       <c r="R130" t="n">
         <v>0.01409973214361761</v>
       </c>
-      <c r="S130" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U130" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -22556,17 +19991,7 @@
       </c>
       <c r="AP130" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ130" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR130" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS130" t="inlineStr">
@@ -22575,12 +20000,7 @@
         </is>
       </c>
       <c r="AT130" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU130" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV130" t="inlineStr">
         <is>
@@ -22704,11 +20124,6 @@
       <c r="R131" t="n">
         <v>0.01639503737629954</v>
       </c>
-      <c r="S131" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U131" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -22726,17 +20141,7 @@
       </c>
       <c r="AP131" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ131" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR131" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS131" t="inlineStr">
@@ -22745,12 +20150,7 @@
         </is>
       </c>
       <c r="AT131" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU131" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV131" t="inlineStr">
         <is>
@@ -22874,11 +20274,6 @@
       <c r="R132" t="n">
         <v>0.02196935008424139</v>
       </c>
-      <c r="S132" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U132" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -22896,17 +20291,7 @@
       </c>
       <c r="AP132" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ132" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR132" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS132" t="inlineStr">
@@ -22915,12 +20300,7 @@
         </is>
       </c>
       <c r="AT132" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU132" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV132" t="inlineStr">
         <is>
@@ -23044,11 +20424,6 @@
       <c r="R133" t="n">
         <v>0.01344393064856563</v>
       </c>
-      <c r="S133" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U133" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -23066,17 +20441,7 @@
       </c>
       <c r="AP133" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ133" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR133" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS133" t="inlineStr">
@@ -23085,12 +20450,7 @@
         </is>
       </c>
       <c r="AT133" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU133" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV133" t="inlineStr">
         <is>
@@ -23214,11 +20574,6 @@
       <c r="R134" t="n">
         <v>0.01836244186145549</v>
       </c>
-      <c r="S134" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U134" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -23236,17 +20591,7 @@
       </c>
       <c r="AP134" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ134" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR134" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS134" t="inlineStr">
@@ -23255,12 +20600,7 @@
         </is>
       </c>
       <c r="AT134" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU134" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV134" t="inlineStr">
         <is>
@@ -23384,11 +20724,6 @@
       <c r="R135" t="n">
         <v>0.0180345411139295</v>
       </c>
-      <c r="S135" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U135" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -23406,17 +20741,7 @@
       </c>
       <c r="AP135" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ135" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR135" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS135" t="inlineStr">
@@ -23425,12 +20750,7 @@
         </is>
       </c>
       <c r="AT135" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU135" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV135" t="inlineStr">
         <is>
@@ -23554,11 +20874,6 @@
       <c r="R136" t="n">
         <v>0.02032984634661144</v>
       </c>
-      <c r="S136" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U136" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -23576,17 +20891,7 @@
       </c>
       <c r="AP136" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ136" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR136" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS136" t="inlineStr">
@@ -23595,12 +20900,7 @@
         </is>
       </c>
       <c r="AT136" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU136" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV136" t="inlineStr">
         <is>
@@ -23724,11 +21024,6 @@
       <c r="R137" t="n">
         <v>0.0324621740050731</v>
       </c>
-      <c r="S137" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U137" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -23746,17 +21041,7 @@
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ137" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR137" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS137" t="inlineStr">
@@ -23765,12 +21050,7 @@
         </is>
       </c>
       <c r="AT137" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU137" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV137" t="inlineStr">
         <is>
@@ -23894,11 +21174,6 @@
       <c r="R138" t="n">
         <v>0.03410167774270306</v>
       </c>
-      <c r="S138" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U138" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -23916,17 +21191,7 @@
       </c>
       <c r="AP138" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ138" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR138" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS138" t="inlineStr">
@@ -23935,12 +21200,7 @@
         </is>
       </c>
       <c r="AT138" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU138" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV138" t="inlineStr">
         <is>
@@ -24064,11 +21324,6 @@
       <c r="R139" t="n">
         <v>0.04131549418827486</v>
       </c>
-      <c r="S139" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U139" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -24086,17 +21341,7 @@
       </c>
       <c r="AP139" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ139" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR139" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS139" t="inlineStr">
@@ -24105,12 +21350,7 @@
         </is>
       </c>
       <c r="AT139" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU139" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV139" t="inlineStr">
         <is>
@@ -24234,11 +21474,6 @@
       <c r="R140" t="n">
         <v>0.03541328073280701</v>
       </c>
-      <c r="S140" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U140" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -24256,17 +21491,7 @@
       </c>
       <c r="AP140" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ140" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR140" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS140" t="inlineStr">
@@ -24275,12 +21500,7 @@
         </is>
       </c>
       <c r="AT140" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU140" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV140" t="inlineStr">
         <is>
@@ -24404,11 +21624,6 @@
       <c r="R141" t="n">
         <v>0.03803648671301495</v>
       </c>
-      <c r="S141" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U141" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -24426,17 +21641,7 @@
       </c>
       <c r="AP141" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ141" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR141" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS141" t="inlineStr">
@@ -24445,12 +21650,7 @@
         </is>
       </c>
       <c r="AT141" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU141" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV141" t="inlineStr">
         <is>
@@ -24574,11 +21774,6 @@
       <c r="R142" t="n">
         <v>0.03311797550012508</v>
       </c>
-      <c r="S142" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U142" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -24596,17 +21791,7 @@
       </c>
       <c r="AP142" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ142" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR142" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS142" t="inlineStr">
@@ -24615,12 +21800,7 @@
         </is>
       </c>
       <c r="AT142" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU142" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV142" t="inlineStr">
         <is>
@@ -24744,11 +21924,6 @@
       <c r="R143" t="n">
         <v>0.02951106727733918</v>
       </c>
-      <c r="S143" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U143" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -24766,17 +21941,7 @@
       </c>
       <c r="AP143" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ143" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR143" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS143" t="inlineStr">
@@ -24785,12 +21950,7 @@
         </is>
       </c>
       <c r="AT143" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU143" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV143" t="inlineStr">
         <is>
@@ -24914,11 +22074,6 @@
       <c r="R144" t="n">
         <v>0.03639698297538499</v>
       </c>
-      <c r="S144" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U144" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -24936,17 +22091,7 @@
       </c>
       <c r="AP144" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ144" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR144" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS144" t="inlineStr">
@@ -24955,12 +22100,7 @@
         </is>
       </c>
       <c r="AT144" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU144" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV144" t="inlineStr">
         <is>
@@ -25084,11 +22224,6 @@
       <c r="R145" t="n">
         <v>0.04721770764374269</v>
       </c>
-      <c r="S145" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U145" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -25106,17 +22241,7 @@
       </c>
       <c r="AP145" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ145" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR145" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS145" t="inlineStr">
@@ -25125,12 +22250,7 @@
         </is>
       </c>
       <c r="AT145" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU145" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV145" t="inlineStr">
         <is>
@@ -25254,11 +22374,6 @@
       <c r="R146" t="n">
         <v>0.02098564784166342</v>
       </c>
-      <c r="S146" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U146" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -25276,17 +22391,7 @@
       </c>
       <c r="AP146" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ146" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR146" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS146" t="inlineStr">
@@ -25295,12 +22400,7 @@
         </is>
       </c>
       <c r="AT146" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU146" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV146" t="inlineStr">
         <is>
@@ -25424,11 +22524,6 @@
       <c r="R147" t="n">
         <v>0.02918316652981319</v>
       </c>
-      <c r="S147" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U147" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -25446,17 +22541,7 @@
       </c>
       <c r="AP147" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ147" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR147" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS147" t="inlineStr">
@@ -25465,12 +22550,7 @@
         </is>
       </c>
       <c r="AT147" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU147" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV147" t="inlineStr">
         <is>
@@ -25594,11 +22674,6 @@
       <c r="R148" t="n">
         <v>0.04197129568332684</v>
       </c>
-      <c r="S148" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U148" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -25616,17 +22691,7 @@
       </c>
       <c r="AP148" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ148" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR148" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS148" t="inlineStr">
@@ -25635,12 +22700,7 @@
         </is>
       </c>
       <c r="AT148" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU148" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV148" t="inlineStr">
         <is>
@@ -25764,11 +22824,6 @@
       <c r="R149" t="n">
         <v>0.07869617940623783</v>
       </c>
-      <c r="S149" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U149" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -25786,17 +22841,7 @@
       </c>
       <c r="AP149" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ149" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR149" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS149" t="inlineStr">
@@ -25805,12 +22850,7 @@
         </is>
       </c>
       <c r="AT149" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU149" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV149" t="inlineStr">
         <is>
@@ -25934,11 +22974,6 @@
       <c r="R150" t="n">
         <v>0.04852931063384665</v>
       </c>
-      <c r="S150" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U150" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -25956,17 +22991,7 @@
       </c>
       <c r="AP150" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ150" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR150" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS150" t="inlineStr">
@@ -25975,12 +23000,7 @@
         </is>
       </c>
       <c r="AT150" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU150" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV150" t="inlineStr">
         <is>
@@ -26104,11 +23124,6 @@
       <c r="R151" t="n">
         <v>0.0757450726785039</v>
       </c>
-      <c r="S151" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U151" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -26126,17 +23141,7 @@
       </c>
       <c r="AP151" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ151" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR151" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS151" t="inlineStr">
@@ -26145,12 +23150,7 @@
         </is>
       </c>
       <c r="AT151" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU151" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV151" t="inlineStr">
         <is>
@@ -26274,11 +23274,6 @@
       <c r="R152" t="n">
         <v>0.06426854651509423</v>
       </c>
-      <c r="S152" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U152" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -26296,17 +23291,7 @@
       </c>
       <c r="AP152" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ152" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR152" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS152" t="inlineStr">
@@ -26315,12 +23300,7 @@
         </is>
       </c>
       <c r="AT152" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU152" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV152" t="inlineStr">
         <is>
@@ -26444,11 +23424,6 @@
       <c r="R153" t="n">
         <v>0.0544315240893145</v>
       </c>
-      <c r="S153" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U153" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -26466,17 +23441,7 @@
       </c>
       <c r="AP153" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ153" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR153" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS153" t="inlineStr">
@@ -26485,12 +23450,7 @@
         </is>
       </c>
       <c r="AT153" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU153" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV153" t="inlineStr">
         <is>
@@ -26614,11 +23574,6 @@
       <c r="R154" t="n">
         <v>0.09935392650037525</v>
       </c>
-      <c r="S154" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U154" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -26636,17 +23591,7 @@
       </c>
       <c r="AP154" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ154" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR154" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS154" t="inlineStr">
@@ -26655,12 +23600,7 @@
         </is>
       </c>
       <c r="AT154" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU154" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV154" t="inlineStr">
         <is>
@@ -26784,11 +23724,6 @@
       <c r="R155" t="n">
         <v>0.05311992109921053</v>
       </c>
-      <c r="S155" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U155" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -26806,17 +23741,7 @@
       </c>
       <c r="AP155" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ155" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR155" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS155" t="inlineStr">
@@ -26825,12 +23750,7 @@
         </is>
       </c>
       <c r="AT155" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU155" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV155" t="inlineStr">
         <is>
@@ -26954,11 +23874,6 @@
       <c r="R156" t="n">
         <v>0.03147847176249512</v>
       </c>
-      <c r="S156" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U156" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -26976,17 +23891,7 @@
       </c>
       <c r="AP156" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ156" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR156" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS156" t="inlineStr">
@@ -26995,12 +23900,7 @@
         </is>
       </c>
       <c r="AT156" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU156" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV156" t="inlineStr">
         <is>
@@ -27124,11 +24024,6 @@
       <c r="R157" t="n">
         <v>0.04155527708361572</v>
       </c>
-      <c r="S157" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U157" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -27146,17 +24041,7 @@
       </c>
       <c r="AP157" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ157" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR157" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS157" t="inlineStr">
@@ -27165,12 +24050,7 @@
         </is>
       </c>
       <c r="AT157" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU157" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV157" t="inlineStr">
         <is>
@@ -27294,11 +24174,6 @@
       <c r="R158" t="n">
         <v>0.03343901202822203</v>
       </c>
-      <c r="S158" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U158" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -27316,17 +24191,7 @@
       </c>
       <c r="AP158" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ158" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR158" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS158" t="inlineStr">
@@ -27335,12 +24200,7 @@
         </is>
       </c>
       <c r="AT158" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU158" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV158" t="inlineStr">
         <is>
@@ -27464,11 +24324,6 @@
       <c r="R159" t="n">
         <v>0.01168742167976692</v>
       </c>
-      <c r="S159" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U159" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -27486,17 +24341,7 @@
       </c>
       <c r="AP159" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ159" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR159" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS159" t="inlineStr">
@@ -27505,12 +24350,7 @@
         </is>
       </c>
       <c r="AT159" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU159" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV159" t="inlineStr">
         <is>
@@ -27634,11 +24474,6 @@
       <c r="R160" t="n">
         <v>0.03019250600606455</v>
       </c>
-      <c r="S160" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U160" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -27656,17 +24491,7 @@
       </c>
       <c r="AP160" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ160" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR160" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS160" t="inlineStr">
@@ -27675,12 +24500,7 @@
         </is>
       </c>
       <c r="AT160" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU160" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV160" t="inlineStr">
         <is>
@@ -27804,11 +24624,6 @@
       <c r="R161" t="n">
         <v>0.03603621684594801</v>
       </c>
-      <c r="S161" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U161" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -27826,17 +24641,7 @@
       </c>
       <c r="AP161" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ161" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR161" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS161" t="inlineStr">
@@ -27845,12 +24650,7 @@
         </is>
       </c>
       <c r="AT161" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU161" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV161" t="inlineStr">
         <is>
@@ -27974,11 +24774,6 @@
       <c r="R162" t="n">
         <v>0.06395616863650233</v>
       </c>
-      <c r="S162" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U162" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -27996,17 +24791,7 @@
       </c>
       <c r="AP162" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ162" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR162" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS162" t="inlineStr">
@@ -28015,12 +24800,7 @@
         </is>
       </c>
       <c r="AT162" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU162" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV162" t="inlineStr">
         <is>
@@ -28144,11 +24924,6 @@
       <c r="R163" t="n">
         <v>0.03214040961935904</v>
       </c>
-      <c r="S163" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U163" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -28166,17 +24941,7 @@
       </c>
       <c r="AP163" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ163" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR163" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS163" t="inlineStr">
@@ -28185,12 +24950,7 @@
         </is>
       </c>
       <c r="AT163" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU163" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV163" t="inlineStr">
         <is>
@@ -28314,11 +25074,6 @@
       <c r="R164" t="n">
         <v>0.03506226503930077</v>
       </c>
-      <c r="S164" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U164" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -28336,17 +25091,7 @@
       </c>
       <c r="AP164" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ164" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR164" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS164" t="inlineStr">
@@ -28355,12 +25100,7 @@
         </is>
       </c>
       <c r="AT164" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU164" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV164" t="inlineStr">
         <is>
@@ -28484,11 +25224,6 @@
       <c r="R165" t="n">
         <v>0.03084180721049605</v>
       </c>
-      <c r="S165" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U165" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -28506,17 +25241,7 @@
       </c>
       <c r="AP165" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ165" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR165" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS165" t="inlineStr">
@@ -28525,12 +25250,7 @@
         </is>
       </c>
       <c r="AT165" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU165" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV165" t="inlineStr">
         <is>
@@ -28654,11 +25374,6 @@
       <c r="R166" t="n">
         <v>0.05324269876338264</v>
       </c>
-      <c r="S166" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U166" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -28676,17 +25391,7 @@
       </c>
       <c r="AP166" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ166" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR166" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS166" t="inlineStr">
@@ -28695,12 +25400,7 @@
         </is>
       </c>
       <c r="AT166" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU166" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV166" t="inlineStr">
         <is>
@@ -28824,11 +25524,6 @@
       <c r="R167" t="n">
         <v>0.07369568670297476</v>
       </c>
-      <c r="S167" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U167" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -28846,17 +25541,7 @@
       </c>
       <c r="AP167" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ167" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR167" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS167" t="inlineStr">
@@ -28865,12 +25550,7 @@
         </is>
       </c>
       <c r="AT167" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU167" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV167" t="inlineStr">
         <is>
@@ -28994,11 +25674,6 @@
       <c r="R168" t="n">
         <v>0.04252922889026296</v>
       </c>
-      <c r="S168" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U168" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -29016,17 +25691,7 @@
       </c>
       <c r="AP168" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ168" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR168" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS168" t="inlineStr">
@@ -29035,12 +25700,7 @@
         </is>
       </c>
       <c r="AT168" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU168" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV168" t="inlineStr">
         <is>
@@ -29164,11 +25824,6 @@
       <c r="R169" t="n">
         <v>0.03895807226588974</v>
       </c>
-      <c r="S169" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U169" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -29186,17 +25841,7 @@
       </c>
       <c r="AP169" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ169" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR169" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS169" t="inlineStr">
@@ -29205,12 +25850,7 @@
         </is>
       </c>
       <c r="AT169" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU169" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV169" t="inlineStr">
         <is>
@@ -29334,11 +25974,6 @@
       <c r="R170" t="n">
         <v>0.02824460239277006</v>
       </c>
-      <c r="S170" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U170" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -29356,17 +25991,7 @@
       </c>
       <c r="AP170" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ170" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR170" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS170" t="inlineStr">
@@ -29375,12 +26000,7 @@
         </is>
       </c>
       <c r="AT170" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU170" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV170" t="inlineStr">
         <is>
@@ -29504,11 +26124,6 @@
       <c r="R171" t="n">
         <v>0.03668551805037951</v>
       </c>
-      <c r="S171" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U171" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -29526,17 +26141,7 @@
       </c>
       <c r="AP171" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ171" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR171" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS171" t="inlineStr">
@@ -29545,12 +26150,7 @@
         </is>
       </c>
       <c r="AT171" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU171" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV171" t="inlineStr">
         <is>
@@ -29674,11 +26274,6 @@
       <c r="R172" t="n">
         <v>0.03863342166367399</v>
       </c>
-      <c r="S172" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U172" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -29696,17 +26291,7 @@
       </c>
       <c r="AP172" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ172" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR172" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS172" t="inlineStr">
@@ -29715,12 +26300,7 @@
         </is>
       </c>
       <c r="AT172" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU172" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV172" t="inlineStr">
         <is>
@@ -29844,11 +26424,6 @@
       <c r="R173" t="n">
         <v>0.03701016865259525</v>
       </c>
-      <c r="S173" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U173" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -29866,17 +26441,7 @@
       </c>
       <c r="AP173" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ173" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR173" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS173" t="inlineStr">
@@ -29885,12 +26450,7 @@
         </is>
       </c>
       <c r="AT173" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU173" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV173" t="inlineStr">
         <is>
@@ -30014,11 +26574,6 @@
       <c r="R174" t="n">
         <v>0.0305171566082803</v>
       </c>
-      <c r="S174" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U174" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -30036,17 +26591,7 @@
       </c>
       <c r="AP174" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ174" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR174" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS174" t="inlineStr">
@@ -30055,12 +26600,7 @@
         </is>
       </c>
       <c r="AT174" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU174" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV174" t="inlineStr">
         <is>
@@ -30184,11 +26724,6 @@
       <c r="R175" t="n">
         <v>0.02727065058612282</v>
       </c>
-      <c r="S175" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U175" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -30206,17 +26741,7 @@
       </c>
       <c r="AP175" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ175" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR175" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS175" t="inlineStr">
@@ -30225,12 +26750,7 @@
         </is>
       </c>
       <c r="AT175" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU175" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV175" t="inlineStr">
         <is>
@@ -30354,11 +26874,6 @@
       <c r="R176" t="n">
         <v>0.01395997589527716</v>
       </c>
-      <c r="S176" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U176" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -30376,17 +26891,7 @@
       </c>
       <c r="AP176" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ176" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR176" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS176" t="inlineStr">
@@ -30395,12 +26900,7 @@
         </is>
       </c>
       <c r="AT176" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU176" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV176" t="inlineStr">
         <is>
@@ -30524,11 +27024,6 @@
       <c r="R177" t="n">
         <v>0.02434879516618109</v>
       </c>
-      <c r="S177" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U177" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -30546,17 +27041,7 @@
       </c>
       <c r="AP177" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ177" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR177" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS177" t="inlineStr">
@@ -30565,12 +27050,7 @@
         </is>
       </c>
       <c r="AT177" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU177" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV177" t="inlineStr">
         <is>
@@ -30694,11 +27174,6 @@
       <c r="R178" t="n">
         <v>0.02045298793959211</v>
       </c>
-      <c r="S178" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U178" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -30716,17 +27191,7 @@
       </c>
       <c r="AP178" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ178" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR178" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS178" t="inlineStr">
@@ -30735,12 +27200,7 @@
         </is>
       </c>
       <c r="AT178" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU178" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV178" t="inlineStr">
         <is>
@@ -30864,11 +27324,6 @@
       <c r="R179" t="n">
         <v>0.04772363852571493</v>
       </c>
-      <c r="S179" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U179" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -30886,17 +27341,7 @@
       </c>
       <c r="AP179" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ179" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR179" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS179" t="inlineStr">
@@ -30905,12 +27350,7 @@
         </is>
       </c>
       <c r="AT179" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU179" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV179" t="inlineStr">
         <is>
@@ -31034,11 +27474,6 @@
       <c r="R180" t="n">
         <v>0.04772363852571493</v>
       </c>
-      <c r="S180" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U180" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -31056,17 +27491,7 @@
       </c>
       <c r="AP180" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ180" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR180" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS180" t="inlineStr">
@@ -31075,12 +27500,7 @@
         </is>
       </c>
       <c r="AT180" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU180" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV180" t="inlineStr">
         <is>
@@ -31204,11 +27624,6 @@
       <c r="R181" t="n">
         <v>0.07856544573621098</v>
       </c>
-      <c r="S181" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U181" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -31226,17 +27641,7 @@
       </c>
       <c r="AP181" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ181" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR181" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS181" t="inlineStr">
@@ -31245,12 +27650,7 @@
         </is>
       </c>
       <c r="AT181" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU181" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV181" t="inlineStr">
         <is>
@@ -31374,11 +27774,6 @@
       <c r="R182" t="n">
         <v>0.0305171566082803</v>
       </c>
-      <c r="S182" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U182" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -31396,17 +27791,7 @@
       </c>
       <c r="AP182" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ182" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR182" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS182" t="inlineStr">
@@ -31415,12 +27800,7 @@
         </is>
       </c>
       <c r="AT182" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU182" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV182" t="inlineStr">
         <is>
@@ -31544,11 +27924,6 @@
       <c r="R183" t="n">
         <v>0.02597204817725983</v>
       </c>
-      <c r="S183" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U183" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -31566,17 +27941,7 @@
       </c>
       <c r="AP183" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ183" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR183" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS183" t="inlineStr">
@@ -31585,12 +27950,7 @@
         </is>
       </c>
       <c r="AT183" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU183" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV183" t="inlineStr">
         <is>
@@ -31714,11 +28074,6 @@
       <c r="R184" t="n">
         <v>0.02856925299498581</v>
       </c>
-      <c r="S184" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U184" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -31736,17 +28091,7 @@
       </c>
       <c r="AP184" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ184" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR184" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS184" t="inlineStr">
@@ -31755,12 +28100,7 @@
         </is>
       </c>
       <c r="AT184" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU184" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV184" t="inlineStr">
         <is>
@@ -31884,11 +28224,6 @@
       <c r="R185" t="n">
         <v>0.02467344576839684</v>
       </c>
-      <c r="S185" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U185" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -31906,17 +28241,7 @@
       </c>
       <c r="AP185" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ185" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR185" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS185" t="inlineStr">
@@ -31925,12 +28250,7 @@
         </is>
       </c>
       <c r="AT185" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU185" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV185" t="inlineStr">
         <is>
@@ -32054,11 +28374,6 @@
       <c r="R186" t="n">
         <v>0.07499428911183775</v>
       </c>
-      <c r="S186" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U186" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -32076,17 +28391,7 @@
       </c>
       <c r="AP186" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ186" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR186" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS186" t="inlineStr">
@@ -32095,12 +28400,7 @@
         </is>
       </c>
       <c r="AT186" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU186" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV186" t="inlineStr">
         <is>
@@ -32224,11 +28524,6 @@
       <c r="R187" t="n">
         <v>0.09220077102927238</v>
       </c>
-      <c r="S187" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U187" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -32246,17 +28541,7 @@
       </c>
       <c r="AP187" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ187" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR187" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS187" t="inlineStr">
@@ -32265,12 +28550,7 @@
         </is>
       </c>
       <c r="AT187" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU187" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV187" t="inlineStr">
         <is>
@@ -32394,11 +28674,6 @@
       <c r="R188" t="n">
         <v>0.02012833733737637</v>
       </c>
-      <c r="S188" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U188" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -32416,17 +28691,7 @@
       </c>
       <c r="AP188" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ188" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR188" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS188" t="inlineStr">
@@ -32435,12 +28700,7 @@
         </is>
       </c>
       <c r="AT188" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU188" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV188" t="inlineStr">
         <is>
@@ -32564,11 +28824,6 @@
       <c r="R189" t="n">
         <v>0.09285007223370388</v>
       </c>
-      <c r="S189" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U189" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -32586,17 +28841,7 @@
       </c>
       <c r="AP189" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ189" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR189" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS189" t="inlineStr">
@@ -32605,12 +28850,7 @@
         </is>
       </c>
       <c r="AT189" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU189" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV189" t="inlineStr">
         <is>
@@ -32734,11 +28974,6 @@
       <c r="R190" t="n">
         <v>0.07434498790740625</v>
       </c>
-      <c r="S190" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U190" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -32756,17 +28991,7 @@
       </c>
       <c r="AP190" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ190" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR190" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS190" t="inlineStr">
@@ -32775,12 +29000,7 @@
         </is>
       </c>
       <c r="AT190" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU190" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV190" t="inlineStr">
         <is>
@@ -32904,11 +29124,6 @@
       <c r="R191" t="n">
         <v>0.06817662646530705</v>
       </c>
-      <c r="S191" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U191" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -32926,17 +29141,7 @@
       </c>
       <c r="AP191" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ191" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR191" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS191" t="inlineStr">
@@ -32945,12 +29150,7 @@
         </is>
       </c>
       <c r="AT191" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU191" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV191" t="inlineStr">
         <is>
@@ -33074,11 +29274,6 @@
       <c r="R192" t="n">
         <v>0.06038501201212909</v>
       </c>
-      <c r="S192" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U192" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -33096,17 +29291,7 @@
       </c>
       <c r="AP192" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ192" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR192" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS192" t="inlineStr">
@@ -33115,12 +29300,7 @@
         </is>
       </c>
       <c r="AT192" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU192" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV192" t="inlineStr">
         <is>
@@ -33244,11 +29424,6 @@
       <c r="R193" t="n">
         <v>0.05681385538775587</v>
       </c>
-      <c r="S193" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U193" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -33266,17 +29441,7 @@
       </c>
       <c r="AP193" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ193" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR193" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS193" t="inlineStr">
@@ -33285,12 +29450,7 @@
         </is>
       </c>
       <c r="AT193" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU193" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV193" t="inlineStr">
         <is>
@@ -33414,11 +29574,6 @@
       <c r="R194" t="n">
         <v>0.08440915657609444</v>
       </c>
-      <c r="S194" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U194" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -33436,17 +29591,7 @@
       </c>
       <c r="AP194" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ194" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR194" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS194" t="inlineStr">
@@ -33455,12 +29600,7 @@
         </is>
       </c>
       <c r="AT194" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU194" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV194" t="inlineStr">
         <is>
@@ -33584,11 +29724,6 @@
       <c r="R195" t="n">
         <v>0.07499428911183775</v>
       </c>
-      <c r="S195" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U195" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -33606,17 +29741,7 @@
       </c>
       <c r="AP195" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ195" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR195" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS195" t="inlineStr">
@@ -33625,12 +29750,7 @@
         </is>
       </c>
       <c r="AT195" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU195" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV195" t="inlineStr">
         <is>
@@ -33754,11 +29874,6 @@
       <c r="R196" t="n">
         <v>0.05616455418332437</v>
       </c>
-      <c r="S196" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U196" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -33776,17 +29891,7 @@
       </c>
       <c r="AP196" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ196" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR196" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS196" t="inlineStr">
@@ -33795,12 +29900,7 @@
         </is>
       </c>
       <c r="AT196" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU196" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV196" t="inlineStr">
         <is>
@@ -33924,11 +30024,6 @@
       <c r="R197" t="n">
         <v>0.03343901202822203</v>
       </c>
-      <c r="S197" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U197" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -33946,17 +30041,7 @@
       </c>
       <c r="AP197" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ197" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR197" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS197" t="inlineStr">
@@ -33965,12 +30050,7 @@
         </is>
       </c>
       <c r="AT197" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU197" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV197" t="inlineStr">
         <is>
@@ -34094,11 +30174,6 @@
       <c r="R198" t="n">
         <v>0.01720648191743463</v>
       </c>
-      <c r="S198" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U198" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -34116,17 +30191,7 @@
       </c>
       <c r="AP198" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ198" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR198" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS198" t="inlineStr">
@@ -34135,12 +30200,7 @@
         </is>
       </c>
       <c r="AT198" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU198" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV198" t="inlineStr">
         <is>
@@ -34264,11 +30324,6 @@
       <c r="R199" t="n">
         <v>0.01266137348641416</v>
       </c>
-      <c r="S199" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U199" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -34286,17 +30341,7 @@
       </c>
       <c r="AP199" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ199" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR199" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS199" t="inlineStr">
@@ -34305,12 +30350,7 @@
         </is>
       </c>
       <c r="AT199" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU199" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV199" t="inlineStr">
         <is>
@@ -34434,11 +30474,6 @@
       <c r="R200" t="n">
         <v>0.0149339277019244</v>
       </c>
-      <c r="S200" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U200" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -34456,17 +30491,7 @@
       </c>
       <c r="AP200" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ200" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR200" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS200" t="inlineStr">
@@ -34475,12 +30500,7 @@
         </is>
       </c>
       <c r="AT200" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU200" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV200" t="inlineStr">
         <is>
@@ -34604,11 +30624,6 @@
       <c r="R201" t="n">
         <v>0.01266137348641416</v>
       </c>
-      <c r="S201" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U201" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -34626,17 +30641,7 @@
       </c>
       <c r="AP201" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ201" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR201" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS201" t="inlineStr">
@@ -34645,12 +30650,7 @@
         </is>
       </c>
       <c r="AT201" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU201" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV201" t="inlineStr">
         <is>
@@ -34774,11 +30774,6 @@
       <c r="R202" t="n">
         <v>0.007791614453177947</v>
       </c>
-      <c r="S202" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U202" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -34796,17 +30791,7 @@
       </c>
       <c r="AP202" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ202" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR202" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS202" t="inlineStr">
@@ -34815,12 +30800,7 @@
         </is>
       </c>
       <c r="AT202" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU202" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV202" t="inlineStr">
         <is>
@@ -34944,11 +30924,6 @@
       <c r="R203" t="n">
         <v>0.0142846264974929</v>
       </c>
-      <c r="S203" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U203" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -34966,17 +30941,7 @@
       </c>
       <c r="AP203" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ203" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR203" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS203" t="inlineStr">
@@ -34985,12 +30950,7 @@
         </is>
       </c>
       <c r="AT203" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU203" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV203" t="inlineStr">
         <is>
@@ -35114,11 +31074,6 @@
       <c r="R204" t="n">
         <v>0.02434879516618109</v>
       </c>
-      <c r="S204" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U204" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -35136,17 +31091,7 @@
       </c>
       <c r="AP204" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ204" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR204" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS204" t="inlineStr">
@@ -35155,12 +31100,7 @@
         </is>
       </c>
       <c r="AT204" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU204" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV204" t="inlineStr">
         <is>
@@ -35284,11 +31224,6 @@
       <c r="R205" t="n">
         <v>0.01136277107755117</v>
       </c>
-      <c r="S205" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U205" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -35306,17 +31241,7 @@
       </c>
       <c r="AP205" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ205" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR205" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS205" t="inlineStr">
@@ -35325,12 +31250,7 @@
         </is>
       </c>
       <c r="AT205" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU205" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV205" t="inlineStr">
         <is>
@@ -35454,11 +31374,6 @@
       <c r="R206" t="n">
         <v>0.03246506022157478</v>
       </c>
-      <c r="S206" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U206" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -35476,17 +31391,7 @@
       </c>
       <c r="AP206" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ206" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR206" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS206" t="inlineStr">
@@ -35495,12 +31400,7 @@
         </is>
       </c>
       <c r="AT206" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU206" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV206" t="inlineStr">
         <is>
@@ -35624,11 +31524,6 @@
       <c r="R207" t="n">
         <v>0.04512643370798895</v>
       </c>
-      <c r="S207" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U207" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -35646,17 +31541,7 @@
       </c>
       <c r="AP207" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ207" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR207" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS207" t="inlineStr">
@@ -35665,12 +31550,7 @@
         </is>
       </c>
       <c r="AT207" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU207" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV207" t="inlineStr">
         <is>
@@ -35794,11 +31674,6 @@
       <c r="R208" t="n">
         <v>0.07207243369189602</v>
       </c>
-      <c r="S208" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U208" t="inlineStr">
         <is>
           <t>HOLD_US_551bbe64790e80f4928f28d32ba0</t>
@@ -35816,17 +31691,7 @@
       </c>
       <c r="AP208" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ208" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AR208" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS208" t="inlineStr">
@@ -35835,12 +31700,7 @@
         </is>
       </c>
       <c r="AT208" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU208" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV208" t="inlineStr">
         <is>
